--- a/archivos_listados.xlsx
+++ b/archivos_listados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B97"/>
+  <dimension ref="A1:B120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,1152 +443,1428 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DSC_0003.jpg</t>
+          <t>DSC_0001.jpg</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>'DSC_0003.jpg',</t>
+          <t>'DSC_0001.jpg',</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DSC_0007.jpg</t>
+          <t>DSC_0002.jpg</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>'DSC_0007.jpg',</t>
+          <t>'DSC_0002.jpg',</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DSC_0008.jpg</t>
+          <t>DSC_0003.jpg</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>'DSC_0008.jpg',</t>
+          <t>'DSC_0003.jpg',</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DSC_0009.jpg</t>
+          <t>DSC_0005.jpg</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>'DSC_0009.jpg',</t>
+          <t>'DSC_0005.jpg',</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DSC_0010.jpg</t>
+          <t>DSC_0006.jpg</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>'DSC_0010.jpg',</t>
+          <t>'DSC_0006.jpg',</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DSC_0012.jpg</t>
+          <t>DSC_0007.jpg</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>'DSC_0012.jpg',</t>
+          <t>'DSC_0007.jpg',</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DSC_0017.jpg</t>
+          <t>DSC_0008.jpg</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>'DSC_0017.jpg',</t>
+          <t>'DSC_0008.jpg',</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DSC_0019.jpg</t>
+          <t>DSC_0009.jpg</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>'DSC_0019.jpg',</t>
+          <t>'DSC_0009.jpg',</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DSC_0021.jpg</t>
+          <t>DSC_0010.jpg</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>'DSC_0021.jpg',</t>
+          <t>'DSC_0010.jpg',</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DSC_0023.jpg</t>
+          <t>DSC_0011.jpg</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>'DSC_0023.jpg',</t>
+          <t>'DSC_0011.jpg',</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DSC_0025.jpg</t>
+          <t>DSC_0012.jpg</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>'DSC_0025.jpg',</t>
+          <t>'DSC_0012.jpg',</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DSC_0026.jpg</t>
+          <t>DSC_0013.jpg</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>'DSC_0026.jpg',</t>
+          <t>'DSC_0013.jpg',</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DSC_0027.jpg</t>
+          <t>DSC_0014.jpg</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>'DSC_0027.jpg',</t>
+          <t>'DSC_0014.jpg',</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DSC_0028.jpg</t>
+          <t>DSC_0015.jpg</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>'DSC_0028.jpg',</t>
+          <t>'DSC_0015.jpg',</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DSC_0029.jpg</t>
+          <t>DSC_0016.jpg</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>'DSC_0029.jpg',</t>
+          <t>'DSC_0016.jpg',</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DSC_0034.jpg</t>
+          <t>DSC_0017.jpg</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>'DSC_0034.jpg',</t>
+          <t>'DSC_0017.jpg',</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DSC_0036.jpg</t>
+          <t>DSC_0018.jpg</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>'DSC_0036.jpg',</t>
+          <t>'DSC_0018.jpg',</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DSC_0037.jpg</t>
+          <t>DSC_0019.jpg</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>'DSC_0037.jpg',</t>
+          <t>'DSC_0019.jpg',</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DSC_0038.jpg</t>
+          <t>DSC_0020.jpg</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>'DSC_0038.jpg',</t>
+          <t>'DSC_0020.jpg',</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DSC_0039.jpg</t>
+          <t>DSC_0021.jpg</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>'DSC_0039.jpg',</t>
+          <t>'DSC_0021.jpg',</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DSC_0040.jpg</t>
+          <t>DSC_0022.jpg</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>'DSC_0040.jpg',</t>
+          <t>'DSC_0022.jpg',</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DSC_0041.jpg</t>
+          <t>DSC_0023.jpg</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>'DSC_0041.jpg',</t>
+          <t>'DSC_0023.jpg',</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DSC_0042.jpg</t>
+          <t>DSC_0025.jpg</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>'DSC_0042.jpg',</t>
+          <t>'DSC_0025.jpg',</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DSC_0044.jpg</t>
+          <t>DSC_0026.jpg</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>'DSC_0044.jpg',</t>
+          <t>'DSC_0026.jpg',</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DSC_0047.jpg</t>
+          <t>DSC_0027.jpg</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>'DSC_0047.jpg',</t>
+          <t>'DSC_0027.jpg',</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DSC_0048.jpg</t>
+          <t>DSC_0028.jpg</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>'DSC_0048.jpg',</t>
+          <t>'DSC_0028.jpg',</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>DSC_0049.jpg</t>
+          <t>DSC_0031.jpg</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>'DSC_0049.jpg',</t>
+          <t>'DSC_0031.jpg',</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>DSC_0050.jpg</t>
+          <t>DSC_0032.jpg</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>'DSC_0050.jpg',</t>
+          <t>'DSC_0032.jpg',</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>DSC_0052.jpg</t>
+          <t>DSC_0033.jpg</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>'DSC_0052.jpg',</t>
+          <t>'DSC_0033.jpg',</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>DSC_0053.jpg</t>
+          <t>DSC_0034.jpg</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>'DSC_0053.jpg',</t>
+          <t>'DSC_0034.jpg',</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DSC_0056.jpg</t>
+          <t>DSC_0036.jpg</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>'DSC_0056.jpg',</t>
+          <t>'DSC_0036.jpg',</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>DSC_0058.jpg</t>
+          <t>DSC_0037.jpg</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>'DSC_0058.jpg',</t>
+          <t>'DSC_0037.jpg',</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>DSC_0060.jpg</t>
+          <t>DSC_0039.jpg</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>'DSC_0060.jpg',</t>
+          <t>'DSC_0039.jpg',</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>DSC_0061.jpg</t>
+          <t>DSC_0041.jpg</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>'DSC_0061.jpg',</t>
+          <t>'DSC_0041.jpg',</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DSC_0062.jpg</t>
+          <t>DSC_0043.jpg</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>'DSC_0062.jpg',</t>
+          <t>'DSC_0043.jpg',</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>DSC_0063.jpg</t>
+          <t>DSC_0044.jpg</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>'DSC_0063.jpg',</t>
+          <t>'DSC_0044.jpg',</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DSC_0064.jpg</t>
+          <t>DSC_0053.jpg</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>'DSC_0064.jpg',</t>
+          <t>'DSC_0053.jpg',</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DSC_0065.jpg</t>
+          <t>DSC_0055.jpg</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>'DSC_0065.jpg',</t>
+          <t>'DSC_0055.jpg',</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DSC_0066.jpg</t>
+          <t>DSC_0057.jpg</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>'DSC_0066.jpg',</t>
+          <t>'DSC_0057.jpg',</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>DSC_0067.jpg</t>
+          <t>DSC_0058.jpg</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>'DSC_0067.jpg',</t>
+          <t>'DSC_0058.jpg',</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DSC_0069.jpg</t>
+          <t>DSC_0059.jpg</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>'DSC_0069.jpg',</t>
+          <t>'DSC_0059.jpg',</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DSC_0070.jpg</t>
+          <t>DSC_0061.jpg</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>'DSC_0070.jpg',</t>
+          <t>'DSC_0061.jpg',</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DSC_0071.jpg</t>
+          <t>DSC_0063.jpg</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>'DSC_0071.jpg',</t>
+          <t>'DSC_0063.jpg',</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>DSC_0072.jpg</t>
+          <t>DSC_0066.jpg</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>'DSC_0072.jpg',</t>
+          <t>'DSC_0066.jpg',</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DSC_0073.jpg</t>
+          <t>DSC_0067.jpg</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>'DSC_0073.jpg',</t>
+          <t>'DSC_0067.jpg',</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>DSC_0074.jpg</t>
+          <t>DSC_0068.jpg</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>'DSC_0074.jpg',</t>
+          <t>'DSC_0068.jpg',</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>DSC_0076.jpg</t>
+          <t>DSC_0069.jpg</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>'DSC_0076.jpg',</t>
+          <t>'DSC_0069.jpg',</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>DSC_0077.jpg</t>
+          <t>DSC_0076.jpg</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>'DSC_0077.jpg',</t>
+          <t>'DSC_0076.jpg',</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>DSC_0078.jpg</t>
+          <t>DSC_0077.jpg</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>'DSC_0078.jpg',</t>
+          <t>'DSC_0077.jpg',</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>DSC_0081.jpg</t>
+          <t>DSC_0078.jpg</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>'DSC_0081.jpg',</t>
+          <t>'DSC_0078.jpg',</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>DSC_0082.jpg</t>
+          <t>DSC_0079.jpg</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>'DSC_0082.jpg',</t>
+          <t>'DSC_0079.jpg',</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>DSC_0083.jpg</t>
+          <t>DSC_0080.jpg</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>'DSC_0083.jpg',</t>
+          <t>'DSC_0080.jpg',</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DSC_0084.jpg</t>
+          <t>DSC_0081.jpg</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>'DSC_0084.jpg',</t>
+          <t>'DSC_0081.jpg',</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>DSC_0085.jpg</t>
+          <t>DSC_0082.jpg</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>'DSC_0085.jpg',</t>
+          <t>'DSC_0082.jpg',</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>DSC_0086.jpg</t>
+          <t>DSC_0083.jpg</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>'DSC_0086.jpg',</t>
+          <t>'DSC_0083.jpg',</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>DSC_0087.jpg</t>
+          <t>DSC_0084.jpg</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>'DSC_0087.jpg',</t>
+          <t>'DSC_0084.jpg',</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>DSC_0088.jpg</t>
+          <t>DSC_0085.jpg</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>'DSC_0088.jpg',</t>
+          <t>'DSC_0085.jpg',</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>DSC_0089.jpg</t>
+          <t>DSC_0086.jpg</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>'DSC_0089.jpg',</t>
+          <t>'DSC_0086.jpg',</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>DSC_0090.jpg</t>
+          <t>DSC_0087.jpg</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>'DSC_0090.jpg',</t>
+          <t>'DSC_0087.jpg',</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>DSC_0092.jpg</t>
+          <t>DSC_0089.jpg</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>'DSC_0092.jpg',</t>
+          <t>'DSC_0089.jpg',</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>DSC_0093.jpg</t>
+          <t>DSC_0091.jpg</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>'DSC_0093.jpg',</t>
+          <t>'DSC_0091.jpg',</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>DSC_0094.jpg</t>
+          <t>DSC_0092.jpg</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>'DSC_0094.jpg',</t>
+          <t>'DSC_0092.jpg',</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>DSC_0100.jpg</t>
+          <t>DSC_0094.jpg</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>'DSC_0100.jpg',</t>
+          <t>'DSC_0094.jpg',</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>DSC_0102.jpg</t>
+          <t>DSC_0095.jpg</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>'DSC_0102.jpg',</t>
+          <t>'DSC_0095.jpg',</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>DSC_0103.jpg</t>
+          <t>DSC_0096.jpg</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>'DSC_0103.jpg',</t>
+          <t>'DSC_0096.jpg',</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>DSC_0104.jpg</t>
+          <t>DSC_0097.jpg</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>'DSC_0104.jpg',</t>
+          <t>'DSC_0097.jpg',</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>DSC_0106.jpg</t>
+          <t>DSC_0098.jpg</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>'DSC_0106.jpg',</t>
+          <t>'DSC_0098.jpg',</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>DSC_0110.jpg</t>
+          <t>DSC_0101.jpg</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>'DSC_0110.jpg',</t>
+          <t>'DSC_0101.jpg',</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>DSC_0112.jpg</t>
+          <t>DSC_0102.jpg</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>'DSC_0112.jpg',</t>
+          <t>'DSC_0102.jpg',</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>DSC_0118.jpg</t>
+          <t>DSC_0103.jpg</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>'DSC_0118.jpg',</t>
+          <t>'DSC_0103.jpg',</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>DSC_0122.jpg</t>
+          <t>DSC_0104.jpg</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>'DSC_0122.jpg',</t>
+          <t>'DSC_0104.jpg',</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>DSC_0128.jpg</t>
+          <t>DSC_0105.jpg</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>'DSC_0128.jpg',</t>
+          <t>'DSC_0105.jpg',</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>DSC_0130.jpg</t>
+          <t>DSC_0106.jpg</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>'DSC_0130.jpg',</t>
+          <t>'DSC_0106.jpg',</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>DSC_0131.jpg</t>
+          <t>DSC_0107.jpg</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>'DSC_0131.jpg',</t>
+          <t>'DSC_0107.jpg',</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>DSC_0134.jpg</t>
+          <t>DSC_0108.jpg</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>'DSC_0134.jpg',</t>
+          <t>'DSC_0108.jpg',</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>DSC_0135.jpg</t>
+          <t>DSC_0109.jpg</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>'DSC_0135.jpg',</t>
+          <t>'DSC_0109.jpg',</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>DSC_0136.jpg</t>
+          <t>DSC_0110.jpg</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>'DSC_0136.jpg',</t>
+          <t>'DSC_0110.jpg',</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>DSC_0137.jpg</t>
+          <t>DSC_0111.jpg</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>'DSC_0137.jpg',</t>
+          <t>'DSC_0111.jpg',</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>DSC_0138.jpg</t>
+          <t>DSC_0112.jpg</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>'DSC_0138.jpg',</t>
+          <t>'DSC_0112.jpg',</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>DSC_0140.jpg</t>
+          <t>DSC_0118.jpg</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>'DSC_0140.jpg',</t>
+          <t>'DSC_0118.jpg',</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>DSC_0141.jpg</t>
+          <t>DSC_0120.jpg</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>'DSC_0141.jpg',</t>
+          <t>'DSC_0120.jpg',</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>DSC_0144.jpg</t>
+          <t>DSC_0121.jpg</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>'DSC_0144.jpg',</t>
+          <t>'DSC_0121.jpg',</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>DSC_0146.jpg</t>
+          <t>DSC_0124.jpg</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>'DSC_0146.jpg',</t>
+          <t>'DSC_0124.jpg',</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>DSC_0147.jpg</t>
+          <t>DSC_0125.jpg</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>'DSC_0147.jpg',</t>
+          <t>'DSC_0125.jpg',</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>DSC_0148.jpg</t>
+          <t>DSC_0126.jpg</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>'DSC_0148.jpg',</t>
+          <t>'DSC_0126.jpg',</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>DSC_0151.jpg</t>
+          <t>DSC_0130.jpg</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>'DSC_0151.jpg',</t>
+          <t>'DSC_0130.jpg',</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>DSC_0152.jpg</t>
+          <t>DSC_0131.jpg</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>'DSC_0152.jpg',</t>
+          <t>'DSC_0131.jpg',</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>DSC_0153.jpg</t>
+          <t>DSC_0132.jpg</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>'DSC_0153.jpg',</t>
+          <t>'DSC_0132.jpg',</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>DSC_0155.jpg</t>
+          <t>DSC_0133.jpg</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>'DSC_0155.jpg',</t>
+          <t>'DSC_0133.jpg',</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>DSC_0157.jpg</t>
+          <t>DSC_0134.jpg</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>'DSC_0157.jpg',</t>
+          <t>'DSC_0134.jpg',</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>DSC_0158.jpg</t>
+          <t>DSC_0135.jpg</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>'DSC_0158.jpg',</t>
+          <t>'DSC_0135.jpg',</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>DSC_0160.jpg</t>
+          <t>DSC_0137.jpg</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>'DSC_0160.jpg',</t>
+          <t>'DSC_0137.jpg',</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>DSC_0161.jpg</t>
+          <t>DSC_0143.jpg</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>'DSC_0161.jpg',</t>
+          <t>'DSC_0143.jpg',</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>DSC_0162.jpg</t>
+          <t>DSC_0144.jpg</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>'DSC_0162.jpg',</t>
+          <t>'DSC_0144.jpg',</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>DSC_0163.jpg</t>
+          <t>DSC_0147.jpg</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>'DSC_0163.jpg',</t>
+          <t>'DSC_0147.jpg',</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>DSC_0164.jpg</t>
+          <t>DSC_0148.jpg</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>'DSC_0164.jpg',</t>
+          <t>'DSC_0148.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>DSC_0153.jpg</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>'DSC_0153.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>DSC_0154.jpg</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>'DSC_0154.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>DSC_0156.jpg</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>'DSC_0156.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>DSC_0157.jpg</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>'DSC_0157.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>DSC_0160.jpg</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>'DSC_0160.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>DSC_0165.jpg</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>'DSC_0165.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>DSC_0175.jpg</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>'DSC_0175.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>DSC_0176.jpg</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>'DSC_0176.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>DSC_0177.jpg</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>'DSC_0177.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>DSC_0180.jpg</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>'DSC_0180.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>DSC_0185.jpg</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>'DSC_0185.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>DSC_0188.jpg</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>'DSC_0188.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>DSC_0189.jpg</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>'DSC_0189.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>DSC_0191.jpg</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>'DSC_0191.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>DSC_0196.jpg</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>'DSC_0196.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>DSC_0197.jpg</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>'DSC_0197.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>DSC_0201.jpg</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>'DSC_0201.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>DSC_0202.jpg</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>'DSC_0202.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>DSC_0214.jpg</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>'DSC_0214.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>DSC_0216.jpg</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>'DSC_0216.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>DSC_0217.jpg</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>'DSC_0217.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>DSC_0218.jpg</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>'DSC_0218.jpg',</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>DSC_0219.jpg</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>'DSC_0219.jpg',</t>
         </is>
       </c>
     </row>
